--- a/dugnad/sjekkpakker/SIK-17.xlsx
+++ b/dugnad/sjekkpakker/SIK-17.xlsx
@@ -29,12 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="140">
   <si>
     <t>Sjekkpakke SIK-17: Sabotasje, hybride angrep og kritisk infrastruktur</t>
   </si>
   <si>
-    <t>Laget 2026-10-27 · 12 påstander · Uregulert KI (arbeidstittel)</t>
+    <t>Laget 2026-10-27 · 15 påstander · Uregulert KI (arbeidstittel)</t>
   </si>
   <si>
     <t>Sjekket av</t>
@@ -172,7 +172,7 @@
     <t>Du kan bruke KI til å finne kilder, oppsummere og peke deg til rett sted i kilden. Men selve sjekken gjør du selv ved å lese originalen. Uten menneskelig verifisering er dugnaden verdiløs.</t>
   </si>
   <si>
-    <t>Privatpersoner navngis aldri.</t>
+    <t>Privatpersoner i privat rolle navngis aldri. Forskere og fagpersoner som uttaler seg offentlig i fagrollen sin, kan navngis.</t>
   </si>
   <si>
     <t>Spørsmål?</t>
@@ -244,9 +244,9 @@
     <t>PST (årlig) – [Åpne trusselvurderinger] · PST</t>
   </si>
   <si>
-    <t xml:space="preserve">Bremanger (2025): angripere åpnet en ventil ved en demning; PST har knyttet hendelsen til prorussiske aktører [K0068] (sjekk). Ikke et KI-angrep – men det viser hvor sårbar driftsteknologien er.
+    <t xml:space="preserve">Bremanger (2025): en prorussisk hacktivistgruppe fikk tilgang via fjernaksess og åpnet ventilene ved en demning. De sto åpne i fire timer og slapp ut om lag 500 liter vann i sekundet [K1216]. PST har knyttet hendelsen til prorussiske aktører [K0068]. Ikke et KI-angrep – men det viser hvor sårbar driftsteknologien er.
 Norsk sårbarhet: Norge er Europas viktigste gassleverandør og har omfattende undersjøisk infrastruktur – rørledninger, strøm- og datakabler [K0068] [K0069]. Referansepunkter: Svalbard-kabelen (2022) [K1148], Nord Stream (2022) og skadene i Østersjøen (2023–24) [K1149] (sjekk).
-Angrep på kritisk infrastruktur og driftssystemer: demningen i Bremanger (2025) – angripere åpnet en ventil; PST har knyttet hendelsen til prorussiske aktører (sjekk) [K0068]. Ikke et KI-angrep, men viser sårbar driftsteknologi; KI senker terskelen.</t>
+Angrep på kritisk infrastruktur og driftssystemer: demningen i Bremanger (2025) – angripere åpnet en ventil; PST har knyttet hendelsen til prorussiske aktører [K0068] [K1216]. Ikke et KI-angrep, men viser sårbar driftsteknologi; KI senker terskelen.</t>
   </si>
   <si>
     <t>ikke verifisert · Brukes også om enkeltaktører og radikalisering · Eksistens (2026-10-25): usikker – Generell beskrivelse – må velges av et menneske. Agentens kandidat: Politiets sikkerhetstjeneste (PST), «Nasjonal trusselvurdering 2026», 2026, https://www.pst.no/wp-content/uploads/2026/02/Nasjonal-trusselvurdering-2026.pdf. Årlig serie; registeret angir ikke år – valgt nyeste. KI-avsnittet ikke be</t>
@@ -321,12 +321,29 @@
     <t>https://www.pv-magazine.com/2025/05/14/hidden-devices-found-in-chinese-made-inverters-in-the-us-reports-reuters/</t>
   </si>
   <si>
-    <t>Innebygd sabotasjeevne: utstyr som fjernoppdateres eller styres fra skyen, kan stanses av leverandøren – eller staten bak den. Ruters test av elbusser (2025) viste at produsenten kunne fjernstyre eller stanse bussene (SIK-07); det er rapportert om uforklarlige kommunikasjonsenheter i kinesiske solcelle-invertere [K0217] (sjekk).</t>
+    <t>Ruters test av elbusser (2025) viste at produsenten kunne fjernstyre eller stanse bussene (SIK-07); det er funnet udokumentert kommunikasjonsutstyr i kinesiske solcelle-invertere og batterier i USA, og det er gjort funn i strømnettet i Danmark [K0217] [K1216].</t>
   </si>
   <si>
     <t>ikke verifisert · Lagt til 2026-10-13, ikke fra disposisjonen. Fra hukommelsen – sjekk om saken og detaljene stemmer. · Eksistens (2026-10-25): funnet – Bare omtale funnet (pv magazine, 14. mai 2025, om Reuters-saken); Reuters-artikkelens egen tittel ikke sett. Senere DOE-vurdering fant «no definitive evidence», jf. pv-magazine-india.</t>
   </si>
   <si>
+    <t>K1216</t>
+  </si>
+  <si>
+    <t>NSM (2026) – Risiko 2026. Dagens valg – morgendagens risiko · NSM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bremanger (2025): en prorussisk hacktivistgruppe fikk tilgang via fjernaksess og åpnet ventilene ved en demning. De sto åpne i fire timer og slapp ut om lag 500 liter vann i sekundet [K1216]. PST har knyttet hendelsen til prorussiske aktører [K0068]. Ikke et KI-angrep – men det viser hvor sårbar driftsteknologien er.
+Myndighetene venter KI-angrep: «Både NSM og PST forventer at norske virksomheter i løpet av 2026 blir utsatt for cyberoperasjoner hvor KI-verktøy spiller en viktig rolle», og mindre kompetente aktører får evne til operasjoner som før krevde høy teknisk kompetanse [K1216].
+Ruters test av elbusser (2025) viste at produsenten kunne fjernstyre eller stanse bussene (SIK-07); det er funnet udokumentert kommunikasjonsutstyr i kinesiske solcelle-invertere og batterier i USA, og det er gjort funn i strømnettet i Danmark [K0217] [K1216].
+NSM viser til den første cyberoperasjonen «tilnærmet fullstendig orkestrert av kunstig intelligens» (2025) [K1216].
+Digitalsikkerhetsloven og sikkerhetsloven dekker virksomheter [K1150] [K0010], ikke utstyr som kjøpes inn fritt. Digitalsikkerhetsloven trådte i kraft i oktober 2025, omfatter også driftsteknologi og krever varsling innen 24 timer [K1216] (sjekk status for NIS2 og direktivet om kritiske enheters motstandsdyktighet, CER, i EØS).
+Angrep på kritisk infrastruktur og driftssystemer: demningen i Bremanger (2025) – angripere åpnet en ventil; PST har knyttet hendelsen til prorussiske aktører [K0068] [K1216]. Ikke et KI-angrep, men viser sårbar driftsteknologi; KI senker terskelen.</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02). Selve rapporten (K1163 er omtale i Altinget).</t>
+  </si>
+  <si>
     <t>SIK-17.P07</t>
   </si>
   <si>
@@ -342,7 +359,7 @@
     <t>Feilen ser ut som en normal beslutning – i automatiserte vedtak (RET-02), beredskapsvurderinger (SIK-07) og alt som bygger på forgiftede data (SIK-12). Automasjonsbias gjør at ingen stusser (RET-04, TVG-03) [K0176] [K0193].</t>
   </si>
   <si>
-    <t xml:space="preserve">ikke verifisert · Eksistens (2026-10-25): usikker – Årlig serie uten oppgitt år; ifølge søket ble «Nasjonalt digitalt risikobilde» fra 2025 slått sammen med NSMs rapport «Risiko». Kandidater: NSM «Risiko 2025» (kap. «Det digitale risikobildet») https://regjeringen.no/contentassets/6290dec36c374ee191e5c7dbba18a258/risiko-2025.pdf ; NSM «Risiko 2026 – </t>
+    <t>ikke verifisert · Eksistens (2026-10-25): usikker – Årlig serie uten oppgitt år; ifølge søket ble «Nasjonalt digitalt risikobilde» fra 2025 slått sammen med NSMs rapport «Risiko». Kandidater: NSM «Risiko 2025» (kap. «Det digitale risikobildet») https://regjeringen.no/contentassets/6290dec36c374ee191e5c7dbba18a258/risiko-2025.pdf ; NSM «Risiko 2026 –  Oppdatert 2026-10-27: selve «Risiko 2026» er registrert som K1216.</t>
   </si>
   <si>
     <t>SIK-17.P08</t>
@@ -391,6 +408,57 @@
   </si>
   <si>
     <t>ikke verifisert · Lagt til 2026-10-24 (SIK-17). Sjekk. · Eksistens (2026-10-25): usikker – Generell beskrivelse (flere hendelser 2023–2024). Kandidater: Omtale «Paper: Finnish authorities prevented damage to EstLink 1, Balticconnector» (ERR, 2025) https://news.err.ee/1609561838/paper-finnish-authorities-prevented-damage-to-estlink-1-balticconnector ; «Finnish publication: Estlink 1, Balti</t>
+  </si>
+  <si>
+    <t>SIK-17.P13</t>
+  </si>
+  <si>
+    <t>NSM og PST forventer at norske virksomheter i 2026 blir utsatt for cyberoperasjoner der KI-verktøy spiller en viktig rolle</t>
+  </si>
+  <si>
+    <t>SIK-17.P14</t>
+  </si>
+  <si>
+    <t>NSM hevet det nasjonale cyberrisikonivået til HØYT i oktober 2026 etter en tredobling av vellykkede cyberoperasjoner</t>
+  </si>
+  <si>
+    <t>K1201</t>
+  </si>
+  <si>
+    <t>NSM (2026) – NSM hever det nasjonale cyberrisikonivået til HØYT · nsm.no</t>
+  </si>
+  <si>
+    <t>https://nsm.no/aktuelt/nsm-hever-det-nasjonale-cyberrisikonivaet-til-hoyt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risikonivået er hevet: 27. oktober 2026 hevet NSM det nasjonale cyberrisikonivået til HØYT, etter en tredobling av vellykkede cyberoperasjoner mot norske virksomheter det siste halvåret. NSM knytter ikke tredoblingen til KI, men vurderer KI i cyberoperasjoner som en alvorlig risiko som trekker vurderingen opp [K1201].
+Nå bekreftet av myndighetene: NSM skriver at KI «finner sårbarheter raskere enn det mennesker har vært i stand til» [K1201].
+Ikke dokumentert i Norge ennå: NSM vurderer KI i cyberoperasjoner som en alvorlig risiko, men skriver at slik bruk ikke er dokumentert i Norge [K1201].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-27 (REG-02). Publisert 27.10.2026.</t>
+  </si>
+  <si>
+    <t>SIK-17.P15</t>
+  </si>
+  <si>
+    <t>KI gjør at tiden fra en sårbarhet oppdages til den utnyttes, er vesentlig kortere enn før</t>
+  </si>
+  <si>
+    <t>K0262</t>
+  </si>
+  <si>
+    <t>Finanstilsynet (2026) – [Risiko- og sårbarhetsanalyse 2026] · Finanstilsynet</t>
+  </si>
+  <si>
+    <t>https://www.finanstilsynet.no/publikasjoner-og-analyser/risiko--og-sarbarhetsanalyse/risiko--og-sarbarhetsanalyse-2026/risiko--og-sarbarhetsanalyse-2026/risiko--og-sarbarhetsanalyse-2026/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forbeholdet er kvantedatamaskiner: amerikanske myndigheter anslår at de kan knekke dagens kryptering rundt 2030, og data som stjeles i dag, kan dekrypteres senere («harvest now, decrypt later») [K0307] [K0262].
+Finanstilsynet skriver at tiden fra en sårbarhet oppdages til den utnyttes, er «vesentlig kortere enn tidligere», og at sårbarhetsstyring som bygger på manuell prioritering, kanskje ikke gir nok beskyttelse [K0262].</t>
+  </si>
+  <si>
+    <t>ikke verifisert · Lagt til 2026-10-13 fra hullanalysen. · Eksistens (2026-10-25): funnet – ROS 2026 omtalt i søket (presentert 10. juni 2026; nevner økende KI-bruk blant truslene); tittel ikke sett ordrett, sida ikke åpnet, og BankID-poenget er ikke kontrollert.</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1393,26 +1461,22 @@
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="E9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -1427,25 +1491,25 @@
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="E10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1460,10 +1524,10 @@
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>79</v>
@@ -1493,25 +1557,25 @@
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -1526,25 +1590,25 @@
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -1559,25 +1623,25 @@
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -1591,13 +1655,17 @@
       <c r="Q14" s="5"/>
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="C15" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>3</v>
@@ -1606,7 +1674,7 @@
         <v>75</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1619,9 +1687,166 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
+    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q1"/>
-  <mergeCells count="16">
+  <mergeCells count="32">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="L2:L3"/>
@@ -1630,17 +1855,36 @@
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="Q19:Q20"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" sqref="H12:H15">
+  <dataValidations count="9">
+    <dataValidation type="list" allowBlank="1" sqref="H10">
+      <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H13:H20">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H2:H3">
@@ -1649,24 +1893,27 @@
     <dataValidation type="list" allowBlank="1" sqref="H6">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H8:H9">
+    <dataValidation type="list" allowBlank="1" sqref="H8:H10">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J10:J15">
+    <dataValidation type="list" allowBlank="1" sqref="J10:J20">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J15">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J20">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P20">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P20">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E8" r:id="rId1"/>
+    <hyperlink ref="E18" r:id="rId2"/>
+    <hyperlink ref="E19" r:id="rId3"/>
+    <hyperlink ref="E20" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/dugnad/sjekkpakker/SIK-17.xlsx
+++ b/dugnad/sjekkpakker/SIK-17.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="141">
   <si>
     <t>Sjekkpakke SIK-17: Sabotasje, hybride angrep og kritisk infrastruktur</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>NSM (2026) – Risiko 2026. Dagens valg – morgendagens risiko · NSM</t>
+  </si>
+  <si>
+    <t>https://nsm.no/risiko2026</t>
   </si>
   <si>
     <t xml:space="preserve">Bremanger (2025): en prorussisk hacktivistgruppe fikk tilgang via fjernaksess og åpnet ventilene ved en demning. De sto åpne i fire timer og slapp ut om lag 500 liter vann i sekundet [K1216]. PST har knyttet hendelsen til prorussiske aktører [K0068]. Ikke et KI-angrep – men det viser hvor sårbar driftsteknologien er.
@@ -1469,14 +1472,14 @@
       <c r="D9" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>3</v>
+      <c r="E9" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -1491,25 +1494,25 @@
     </row>
     <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1524,10 +1527,10 @@
     </row>
     <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>79</v>
@@ -1557,10 +1560,10 @@
     </row>
     <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>79</v>
@@ -1590,25 +1593,25 @@
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -1623,10 +1626,10 @@
     </row>
     <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>85</v>
@@ -1656,16 +1659,16 @@
     </row>
     <row r="15" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>3</v>
@@ -1674,7 +1677,7 @@
         <v>75</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1691,10 +1694,10 @@
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>3</v>
@@ -1703,7 +1706,7 @@
         <v>75</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -1718,10 +1721,10 @@
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>98</v>
@@ -1729,14 +1732,14 @@
       <c r="D17" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>3</v>
+      <c r="E17" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -1751,25 +1754,25 @@
     </row>
     <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -1784,25 +1787,25 @@
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -1819,19 +1822,19 @@
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -1911,9 +1914,11 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E8" r:id="rId1"/>
-    <hyperlink ref="E18" r:id="rId2"/>
-    <hyperlink ref="E19" r:id="rId3"/>
-    <hyperlink ref="E20" r:id="rId4"/>
+    <hyperlink ref="E9" r:id="rId2"/>
+    <hyperlink ref="E17" r:id="rId3"/>
+    <hyperlink ref="E18" r:id="rId4"/>
+    <hyperlink ref="E19" r:id="rId5"/>
+    <hyperlink ref="E20" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/dugnad/sjekkpakker/SIK-17.xlsx
+++ b/dugnad/sjekkpakker/SIK-17.xlsx
@@ -20,7 +20,7 @@
     <comment ref="B4" authorId="0">
       <text>
         <r>
-          <t>Kallenavn eller GitHub-navn. Det kan bli stående offentlig i kilderegisteret.</t>
+          <t>Navnet du vil stå med offentlig: fullt navn, kallenavn eller GitHub-navn. Det blir stående i kilderegisteret på GitHub og kan ikke fjernes helt i ettertid.</t>
         </r>
       </text>
     </comment>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="143">
   <si>
     <t>Sjekkpakke SIK-17: Sabotasje, hybride angrep og kritisk infrastruktur</t>
   </si>
@@ -64,7 +64,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>Les det som er relevant, og sammenlign med «Rapporten sier». Sett «Status» og skriv kort i «Om kilden» hvordan du sjekket og hva som eventuelt avviker.</t>
+    <t>Les det som er relevant, og sammenlign med «Rapporten sier». Sett «Status», og skriv i «Avvik» hvis noe avviker, ligger bak betalingsmur eller er uventet.</t>
+  </si>
+  <si>
+    <t>Er status «verifisert» eller «delvis», skriv i «Hvor i kilden» hvor det står: side (rapport, bok, artikkel), § og ledd (lov), artikkel og nummer (EU-rett), avsnitt (dom) eller overskrift (nettside). Da kan neste person slå rett opp.</t>
   </si>
   <si>
     <t>4</t>
@@ -94,13 +97,13 @@
     <t>verifisert</t>
   </si>
   <si>
-    <t>Du har åpnet primærkilden, og den sier det påstanden bygger på.</t>
+    <t>Du har lest det relevante i primærkilden, og den sier det påstanden bygger på.</t>
   </si>
   <si>
     <t>delvis</t>
   </si>
   <si>
-    <t>Stemmer, men med avvik. Skriv avviket i «Om kilden».</t>
+    <t>Stemmer, men med avvik. Skriv avviket i «Avvik».</t>
   </si>
   <si>
     <t>sekundær</t>
@@ -157,13 +160,13 @@
     <t>A Aktualitet</t>
   </si>
   <si>
-    <t>Er det fortsatt gyldig? 0 utdatert (motbevist, erstattet, loven endret) eller ikke sjekket · 1 usikker gyldighet (feltet har endret seg mye siden, f.eks. studier av eldre KI-modeller) · 2 gyldig, ingen kjent nyere forskning sier noe annet, uansett alder · 3 fersk (gjelder dagens situasjon) eller bekreftet av nyere forskning. Bekreftelsen kan stå i kommentaren.</t>
+    <t>Er det fortsatt gyldig? 0 utdatert (motbevist, erstattet, lovendring) eller ikke sjekket · 1 usikker gyldighet (feltet har endret seg mye siden, f.eks. studier av eldre KI-modeller) · 2 gyldig, ingen kjent nyere forskning sier noe annet, uansett alder · 3 fersk (gjelder dagens situasjon) eller bekreftet av nyere forskning. Bekreftelsen kan stå i kommentaren.</t>
   </si>
   <si>
     <t>Husk</t>
   </si>
   <si>
-    <t>Aldri dikt opp. Tall, datoer og navn tas fra kilden, ikke fra hukommelsen.</t>
+    <t>Ha integritet.</t>
   </si>
   <si>
     <t>Skill mellom «viser», «tyder på» og «antyder», og mellom én studie og konsensus. En påstand kan ha riktig kilde og likevel si mer enn kilden gjør.</t>
@@ -205,13 +208,16 @@
     <t>Status ▾</t>
   </si>
   <si>
+    <t>Hvor i kilden (s., §, art., avsnitt)</t>
+  </si>
+  <si>
     <t>Riktig eller ny lenke / DOI</t>
   </si>
   <si>
     <t>Fagfelle-vurdert ▾</t>
   </si>
   <si>
-    <t>Om kilden: hvordan du sjekket, hva som avviker</t>
+    <t>Avvik / betalingsmur / uventet</t>
   </si>
   <si>
     <t>E ▾</t>
@@ -468,6 +474,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -500,12 +509,17 @@
       <color rgb="FF1F5FA8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -528,7 +542,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -536,36 +550,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -907,256 +951,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
+    <col min="2" max="2" width="91.45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="B5" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+    </row>
+    <row r="7" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="15" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+    </row>
+    <row r="17" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3" t="s">
+    </row>
+    <row r="19" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="20" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3" t="s">
+    </row>
+    <row r="21" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="23" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="6" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+    </row>
+    <row r="25" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="B26" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="B32" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="3" t="s">
+    <row r="35" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="3" t="s">
+    </row>
+    <row r="37" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="B37" s="13" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1165,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1176,712 +1255,735 @@
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="36" customWidth="1"/>
-    <col min="12" max="16" width="5" customWidth="1"/>
-    <col min="17" max="17" width="40" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="36" customWidth="1"/>
+    <col min="13" max="17" width="5" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" ht="32" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="N1" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="O1" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="P1" s="15" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="Q1" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="R1" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="9" t="s">
+    </row>
+    <row r="2" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="B2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="C2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="D2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
+      <c r="E2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="G2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="D3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="E3" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="G3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+    </row>
+    <row r="4" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="B4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="C4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="D4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="E4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B5" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C5" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+    </row>
+    <row r="6" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="C6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="D6" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-    </row>
-    <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="E6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="G6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B7" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C7" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+    </row>
+    <row r="8" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="C8" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="D8" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="E8" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="F8" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="G8" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="D9" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="E9" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="F9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="G9" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="C10" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="E10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="G10" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+    </row>
+    <row r="11" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B11" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="C11" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+    </row>
+    <row r="12" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B12" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="C12" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="D13" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="E13" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+    </row>
+    <row r="14" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="D14" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="E14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="B15" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="9" t="s">
+      <c r="C15" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9" t="s">
+      <c r="D15" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E15" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="9" t="s">
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+    </row>
+    <row r="16" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="D16" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="E16" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+    </row>
+    <row r="17" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="D17" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="E17" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="F17" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+    </row>
+    <row r="18" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="C18" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="D18" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="E18" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="F18" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="G18" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+    </row>
+    <row r="19" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="B19" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="C19" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="D19" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="E19" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="F19" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+    </row>
+    <row r="20" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="D20" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="E20" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
+      <c r="F20" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:R20"/>
   <mergeCells count="32">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="L8:L9"/>
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="L15:L16"/>
     <mergeCell ref="M15:M16"/>
     <mergeCell ref="N15:N16"/>
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="P15:P16"/>
     <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="L19:L20"/>
     <mergeCell ref="M19:M20"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="P19:P20"/>
     <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" sqref="H10">
@@ -1899,16 +2001,16 @@
     <dataValidation type="list" allowBlank="1" sqref="H8:H10">
       <formula1>"verifisert,delvis,sekundær,ikke funnet,feil"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J10:J20">
+    <dataValidation type="list" allowBlank="1" sqref="K10:K20">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J20">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K20">
       <formula1>"ja,nei,preprint"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L10:P20">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M10:Q20">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:P20">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:Q20">
       <formula1>"0,1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
